--- a/artfynd/A 61872-2019 artfynd.xlsx
+++ b/artfynd/A 61872-2019 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118675770</v>
+        <v>118675771</v>
       </c>
       <c r="B2" t="n">
         <v>94338</v>

--- a/artfynd/A 61872-2019 artfynd.xlsx
+++ b/artfynd/A 61872-2019 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118675771</v>
+        <v>118675770</v>
       </c>
       <c r="B2" t="n">
         <v>94338</v>

--- a/artfynd/A 61872-2019 artfynd.xlsx
+++ b/artfynd/A 61872-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118675770</v>
+        <v>118675771</v>
       </c>
       <c r="B2" t="n">
-        <v>94338</v>
+        <v>94345</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
